--- a/test-data/data.xlsx
+++ b/test-data/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project1\test-data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\newproject\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1610AA7-AD24-46C1-BF72-801B90FD9313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12692B1F-9834-4BAB-98AB-29533D3CC92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="2720" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,17 +30,25 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.makemytrip.com/</t>
+    <t>https://staging.ronspot.ie/admin/dashboard</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -63,13 +71,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -349,15 +360,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
